--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2236-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2236-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87864382-96C2-445B-8340-F6573C047E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2199D6B-8EA5-46A1-80B0-2458CB1B25DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{A35AD044-3270-4F48-AD0B-4D83AE521FF2}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{5D69608D-D9BC-47E5-9D0E-B8A24A823697}"/>
   </bookViews>
   <sheets>
     <sheet name="2236-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1493,25 +1493,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DC6204-0556-4B1A-B2FB-E66B4CE8EDE2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA5C8932-E3F2-4382-AC90-6E756BE05008}">
   <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.5546875" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1665,7 +1665,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2026</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="40">
         <v>2025</v>
       </c>
@@ -1829,7 +1829,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>2024</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="40">
         <v>2023</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="38">
         <v>2022</v>
       </c>
@@ -2271,7 +2271,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>26</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>26</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2021</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>6.77</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>26</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>26</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2020</v>
       </c>
@@ -2659,7 +2659,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2019</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2018</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>3.95</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2017</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>3.31</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2016</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2015</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>4.25</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2014</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40" t="s">
         <v>49</v>
       </c>
